--- a/Undigitized_Records_Form.xlsx
+++ b/Undigitized_Records_Form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{F5846A63-717B-4595-8205-7123A11B21FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05E0C7A4-E498-4197-8135-9A2A7FA3465F}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{F5846A63-717B-4595-8205-7123A11B21FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9357D5AA-441C-4289-A6C2-172D53970BBB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9F2515FD-ACAE-4DB3-A627-796218E8B95C}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Study</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Rough location</t>
   </si>
@@ -479,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09541CA5-EE5E-4961-A8BE-240526C5305A}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
@@ -488,57 +485,52 @@
     <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -550,9 +542,8 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -564,9 +555,8 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -578,9 +568,8 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -592,9 +581,8 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -606,7 +594,6 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
